--- a/2_MRIO/Visualisation/2. Sankeys/2_Sankey_coordinates/Sankey_coordinates_COD.xlsx
+++ b/2_MRIO/Visualisation/2. Sankeys/2_Sankey_coordinates/Sankey_coordinates_COD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/etber_dtu_dk/Documents/Dokumenter/MRIOS/2022 IATRC Annual meeting/Full_article/5. Graphic visualisation/3. Figure_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mitprod-my.sharepoint.com/personal/etber_mit_edu/Documents/Documents/Deforestation_Nature/Forest_Club_SI/2. MRIO/Visualisation/2. Sankeys/2_Sankey_coordinates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{AB413BAB-4098-4B0E-9809-BD123D8FF6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D8BD861-2543-4107-85DB-B0E0FBA0DCFD}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{AB413BAB-4098-4B0E-9809-BD123D8FF6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FC36EC-F810-4594-95A6-847860801373}"/>
   <bookViews>
-    <workbookView xWindow="-67320" yWindow="-3045" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7AACA3EC-67BD-4000-9435-69790F754268}"/>
+    <workbookView xWindow="-29690" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{7AACA3EC-67BD-4000-9435-69790F754268}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,8 +468,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,9 +786,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B661CD3-A5A3-4808-821E-65259E0E2292}">
   <dimension ref="A1:BA24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -948,7 +952,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -961,7 +965,7 @@
       <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>8.8720717771574567</v>
       </c>
       <c r="F2">
@@ -1109,7 +1113,7 @@
         <v>1673.6425593197359</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1122,7 +1126,7 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>452690.13470495702</v>
       </c>
       <c r="F3">
@@ -1270,7 +1274,7 @@
         <v>454882.58255767834</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1283,7 +1287,7 @@
       <c r="D4" t="s">
         <v>52</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>259.7396890000889</v>
       </c>
       <c r="F4">
@@ -1431,7 +1435,7 @@
         <v>1707.4286206141112</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1444,7 +1448,7 @@
       <c r="D5" t="s">
         <v>53</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>332.04076999981299</v>
       </c>
       <c r="F5">
@@ -1592,7 +1596,7 @@
         <v>551.95910445600771</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1605,7 +1609,7 @@
       <c r="D6" t="s">
         <v>54</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>118697.88918089698</v>
       </c>
       <c r="F6">
@@ -1753,7 +1757,7 @@
         <v>98747.299527734547</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1766,7 +1770,7 @@
       <c r="D7" t="s">
         <v>55</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>8387.4586900988525</v>
       </c>
       <c r="F7">
@@ -1914,7 +1918,7 @@
         <v>19144.686155889292</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1927,7 +1931,7 @@
       <c r="D8" t="s">
         <v>56</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>692.89343183961319</v>
       </c>
       <c r="F8">
@@ -2075,7 +2079,7 @@
         <v>3057.636684201655</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2088,7 +2092,7 @@
       <c r="D9" t="s">
         <v>57</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>1782.2871614480887</v>
       </c>
       <c r="F9">
@@ -2236,7 +2240,7 @@
         <v>2807.7348498627534</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2249,7 +2253,7 @@
       <c r="D10" t="s">
         <v>58</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>1561.1073371994523</v>
       </c>
       <c r="F10">
@@ -2397,7 +2401,7 @@
         <v>3923.938744194807</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2410,7 +2414,7 @@
       <c r="D11" t="s">
         <v>59</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>3012.3409534427551</v>
       </c>
       <c r="F11">
@@ -2558,7 +2562,7 @@
         <v>9132.5868974626028</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2571,7 +2575,7 @@
       <c r="D12" t="s">
         <v>60</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>5598.3201760299416</v>
       </c>
       <c r="F12">
@@ -2719,7 +2723,7 @@
         <v>6335.1256049126314</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2732,7 +2736,7 @@
       <c r="D13" t="s">
         <v>61</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>663.5185831233606</v>
       </c>
       <c r="F13">
@@ -2880,7 +2884,7 @@
         <v>1207.1321669705208</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2893,7 +2897,7 @@
       <c r="D14" t="s">
         <v>62</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>488.76972702957426</v>
       </c>
       <c r="F14">
@@ -3041,7 +3045,7 @@
         <v>666.52690658997801</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3054,7 +3058,7 @@
       <c r="D15" t="s">
         <v>63</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>7265.6479825191718</v>
       </c>
       <c r="F15">
@@ -3202,7 +3206,7 @@
         <v>9046.7970830798167</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3215,7 +3219,7 @@
       <c r="D16" t="s">
         <v>64</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>3812.5246210981313</v>
       </c>
       <c r="F16">
@@ -3363,7 +3367,7 @@
         <v>4058.4243386797625</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3376,7 +3380,7 @@
       <c r="D17" t="s">
         <v>65</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>43777.173346026982</v>
       </c>
       <c r="F17">
@@ -3524,7 +3528,7 @@
         <v>24920.101415947072</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3537,7 +3541,7 @@
       <c r="D18" t="s">
         <v>66</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2125.1075064690017</v>
       </c>
       <c r="F18">
@@ -3685,7 +3689,7 @@
         <v>17294.806216597557</v>
       </c>
     </row>
-    <row r="19" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3698,7 +3702,7 @@
       <c r="D19" t="s">
         <v>67</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>38658.680966534521</v>
       </c>
       <c r="F19">
@@ -3846,7 +3850,7 @@
         <v>36092.907431840875</v>
       </c>
     </row>
-    <row r="20" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3859,7 +3863,7 @@
       <c r="D20" t="s">
         <v>68</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>486.97954834089148</v>
       </c>
       <c r="F20">
@@ -4007,7 +4011,7 @@
         <v>1011.5853947512798</v>
       </c>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4020,7 +4024,7 @@
       <c r="D21" t="s">
         <v>69</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>5705.7935684044278</v>
       </c>
       <c r="F21">
@@ -4168,7 +4172,7 @@
         <v>9426.251937538389</v>
       </c>
     </row>
-    <row r="22" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4181,7 +4185,7 @@
       <c r="D22" t="s">
         <v>70</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>28728.476155784079</v>
       </c>
       <c r="F22">
@@ -4329,7 +4333,7 @@
         <v>26237.200086355238</v>
       </c>
     </row>
-    <row r="23" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4342,7 +4346,7 @@
       <c r="D23" t="s">
         <v>71</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>48799.491692096897</v>
       </c>
       <c r="F23">
@@ -4490,7 +4494,7 @@
         <v>40665.010147452384</v>
       </c>
     </row>
-    <row r="24" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4503,7 +4507,7 @@
       <c r="D24" t="s">
         <v>72</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>137.8767736591148</v>
       </c>
       <c r="F24">
@@ -4660,13 +4664,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{125276F1-05EA-427C-941D-75E396FD9E40}">
   <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.54296875" customWidth="1"/>
-    <col min="6" max="6" width="28.54296875" customWidth="1"/>
+    <col min="1" max="1" width="36.5546875" customWidth="1"/>
+    <col min="6" max="6" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>76</v>
       </c>
@@ -4674,7 +4678,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -4682,7 +4686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -4690,7 +4694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>80</v>
       </c>
@@ -4698,7 +4702,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>81</v>
       </c>
@@ -4706,7 +4710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
@@ -4714,7 +4718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -4722,7 +4726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -4730,7 +4734,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -4738,7 +4742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -4746,7 +4750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>86</v>
       </c>
@@ -4762,7 +4766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -4770,7 +4774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>88</v>
       </c>
@@ -4778,7 +4782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -4794,7 +4798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>91</v>
       </c>
@@ -4802,7 +4806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -4810,7 +4814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -4818,7 +4822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>95</v>
       </c>
@@ -4826,7 +4830,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>96</v>
       </c>
@@ -4834,7 +4838,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -4842,7 +4846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>98</v>
       </c>
@@ -4850,7 +4854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>99</v>
       </c>
@@ -4858,7 +4862,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>100</v>
       </c>
@@ -4866,7 +4870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -4874,7 +4878,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -4882,7 +4886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -4890,7 +4894,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>104</v>
       </c>
@@ -4898,7 +4902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>105</v>
       </c>
@@ -4906,7 +4910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>106</v>
       </c>
@@ -4914,7 +4918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>129</v>
       </c>
@@ -4922,7 +4926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -4930,7 +4934,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -4938,7 +4942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>109</v>
       </c>
@@ -4946,7 +4950,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>110</v>
       </c>
@@ -4954,7 +4958,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -4962,7 +4966,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -4970,7 +4974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>113</v>
       </c>
@@ -4978,7 +4982,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>114</v>
       </c>
@@ -4986,7 +4990,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -4994,7 +4998,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -5002,7 +5006,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>117</v>
       </c>
@@ -5010,7 +5014,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>118</v>
       </c>
@@ -5018,7 +5022,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>119</v>
       </c>
@@ -5026,7 +5030,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>120</v>
       </c>
@@ -5034,7 +5038,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>121</v>
       </c>
@@ -5042,7 +5046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>122</v>
       </c>
@@ -5050,7 +5054,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -5058,7 +5062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>124</v>
       </c>
@@ -5066,7 +5070,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>125</v>
       </c>
@@ -5074,7 +5078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>126</v>
       </c>
@@ -5082,7 +5086,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>127</v>
       </c>
